--- a/tests/data/validation/output/comparison.xlsx
+++ b/tests/data/validation/output/comparison.xlsx
@@ -10,6 +10,7 @@
     <sheet name="all" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="area" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ghg" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="protein" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,7 +642,7 @@
         <v>339000</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0003734828355390054</v>
+        <v>0.0003734828355388337</v>
       </c>
     </row>
     <row r="9">
@@ -694,6 +695,84 @@
       </c>
       <c r="F10" t="n">
         <v>0.07890286431387443</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cattle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>436968.1947839</v>
+      </c>
+      <c r="E11" t="n">
+        <v>436968.1999926939</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.192030429500059e-08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Milk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>286820.659125</v>
+      </c>
+      <c r="E12" t="n">
+        <v>286820.659125</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Beef (dairy + suckler)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>150147.5356589</v>
+      </c>
+      <c r="E13" t="n">
+        <v>150147.5408676939</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.469117030522293e-08</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +922,7 @@
         <v>339000</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003734828355390054</v>
+        <v>0.0003734828355388337</v>
       </c>
     </row>
     <row r="6">
@@ -1025,4 +1104,128 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>optigob_ts</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>optigob</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rel_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cattle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>436968.1947839</v>
+      </c>
+      <c r="E2" t="n">
+        <v>436968.1999926939</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.192030429500059e-08</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Milk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>286820.659125</v>
+      </c>
+      <c r="E3" t="n">
+        <v>286820.659125</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Beef (dairy + suckler)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>150147.5356589</v>
+      </c>
+      <c r="E4" t="n">
+        <v>150147.5408676939</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.469117030522293e-08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>